--- a/TDD_examples/CASE_2_ENEA_HTS_CICC/conductor_1_input.xlsx
+++ b/TDD_examples/CASE_2_ENEA_HTS_CICC/conductor_1_input.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHAN" sheetId="2" r:id="Rab90d67455e44c0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STACK" sheetId="5" r:id="Rbb542a2ce1dc4172"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_MIX" sheetId="3" r:id="Rf203c1f1cd524837"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_STAB" sheetId="6" r:id="R8e30cbd58c2c4c5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_JACKET" sheetId="4" r:id="Ra57af0d1ee7f4c69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHAN" sheetId="2" r:id="Rc26bda5c01c14f6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STACK" sheetId="5" r:id="Rcdb4f22e61c44097"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_MIX" sheetId="3" r:id="R82dd7ae1f561479f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_STAB" sheetId="6" r:id="R369982b22ec440cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_JACKET" sheetId="4" r:id="Raba2f166b0fc4063"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,9 +21,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">element of the type "SC+Cu strands"</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">row used to get the correct number of mixed copper-supeconductor strands objects in cell B1 as the sum of values in this row starting from cell D2</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -787,7 +784,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D5" s="48" t="str">
-        <x:v>x coordinate of the barycenter. Not used if flag ITYMESH = -1 in file conductor_grid.</x:v>
+        <x:v>x coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E5" s="45" t="n">
         <x:v>0</x:v>
@@ -840,7 +837,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D6" s="48" t="str">
-        <x:v>y coordinate of the barycenter. Not used if flag ITYMESH = -1 in file conductor_grid.</x:v>
+        <x:v>y coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E6" s="45" t="n">
         <x:v>0</x:v>
@@ -1109,7 +1106,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D11" s="48" t="str">
-        <x:v>VIOD FRACTION OF THE CHANNEL = VOID AREA/TOTALAREA OF THE CHANNEL</x:v>
+        <x:v>VOID FRACTION OF THE CHANNEL = VOID AREA / TOTAL AREA OF THE CHANNEL</x:v>
       </x:c>
       <x:c r="E11" s="44" t="n">
         <x:v>1</x:v>
@@ -2555,8 +2552,8 @@
       <x:c r="A2" s="35"/>
       <x:c r="B2" s="34"/>
       <x:c r="C2" s="34"/>
-      <x:c r="D2" s="36" t="s">
-        <x:v>3</x:v>
+      <x:c r="D2" s="36" t="str">
+        <x:v>Row used to determine the number of mixed copper-superconductor strand objects in cell B1, calculated as the sum of the values in this row starting from cell D2.</x:v>
       </x:c>
       <x:c r="E2" s="32" t="n">
         <x:v>0</x:v>
@@ -3246,7 +3243,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D5" s="48" t="str">
-        <x:v>x coordinate of the barycenter. Not used if flag ITYMESH = -1 in file conductor_grid.</x:v>
+        <x:v>x coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E5" s="45" t="n">
         <x:v>0</x:v>
@@ -3314,7 +3311,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D6" s="48" t="str">
-        <x:v>y coordinate of the barycenter. Not used if flag ITYMESH = -1 in file conductor_grid.</x:v>
+        <x:v>y coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E6" s="45" t="n">
         <x:v>0</x:v>
@@ -3749,7 +3746,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D6" s="48" t="str">
-        <x:v>x coordinate of the barycenter. Not used if flag ITYMESH = -1 in file conductor_grid.</x:v>
+        <x:v>x coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E6" s="45" t="n">
         <x:v>0</x:v>
@@ -3766,7 +3763,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D7" s="48" t="str">
-        <x:v>y coordinate of the barycenter Not used if flag ITYMESH = -1 in file conductor_grid.</x:v>
+        <x:v>y coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E7" s="45" t="n">
         <x:v>0</x:v>
